--- a/data/trans_bre/P14B23-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P14B23-Estudios-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas discapacitantes de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población cuya depresión o ansiedad le limita</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 11,84</t>
+          <t>7,01; 11,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 12,15</t>
+          <t>7,37; 12,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,2</t>
+          <t>2,52; 8,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112,85; 334,58</t>
+          <t>117,35; 334,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>169,5; 484,22</t>
+          <t>168,69; 518,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,64; 139,49</t>
+          <t>21,79; 124,88</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,52</t>
+          <t>1,9; 4,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,31</t>
+          <t>1,98; 4,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,09</t>
+          <t>1,67; 5,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75,24; 304,29</t>
+          <t>72,12; 303,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,37; 291,06</t>
+          <t>81,01; 300,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,08; 259,76</t>
+          <t>52,27; 236,95</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,09</t>
+          <t>-0,15; 2,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,62</t>
+          <t>0,02; 2,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 2,77</t>
+          <t>-0,99; 2,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,46; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-42,56; 1181,59</t>
+          <t>-33,19; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 135,61</t>
+          <t>-26,35; 135,03</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,69</t>
+          <t>4,36; 6,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,7; 5,76</t>
+          <t>3,74; 5,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,9</t>
+          <t>2,26; 4,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148,57; 320,08</t>
+          <t>146,37; 313,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>159,95; 366,16</t>
+          <t>152,07; 338,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,21; 168,64</t>
+          <t>54,11; 164,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P14B23-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P14B23-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>6,11</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,01; 11,8</t>
+          <t>7,14; 11,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 12,59</t>
+          <t>7,01; 12,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,18</t>
+          <t>3,3; 8,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117,35; 334,07</t>
+          <t>121,43; 333,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>168,69; 518,28</t>
+          <t>145,11; 482,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,79; 124,88</t>
+          <t>35,81; 157,49</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>4,1</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>121,34%</t>
+          <t>129,96%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,46</t>
+          <t>1,83; 4,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,31</t>
+          <t>1,95; 4,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,05</t>
+          <t>2,84; 5,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,12; 303,61</t>
+          <t>72,91; 296,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,01; 300,43</t>
+          <t>81,67; 316,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,27; 236,95</t>
+          <t>74,33; 200,41</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,97</t>
+          <t>-0,2; 3,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 2,62</t>
+          <t>-0,05; 2,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,87</t>
+          <t>-1,3; 2,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-88,46; —</t>
+          <t>-83,32; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,19; —</t>
+          <t>-29,77; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,35; 135,03</t>
+          <t>-28,74; 139,2</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,69</t>
+          <t>4,17</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>101,14%</t>
+          <t>108,57%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,53</t>
+          <t>4,48; 6,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 5,65</t>
+          <t>3,73; 5,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,9</t>
+          <t>3,15; 5,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146,37; 313,14</t>
+          <t>151,41; 333,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>152,07; 338,87</t>
+          <t>158,39; 361,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,11; 164,35</t>
+          <t>68,31; 150,02</t>
         </is>
       </c>
     </row>
